--- a/ig/nr-update-patient-ins/CodeSystem-fr-core-cs-v2-3307.xlsx
+++ b/ig/nr-update-patient-ins/CodeSystem-fr-core-cs-v2-3307.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-26T11:00:29+00:00</t>
+    <t>2024-02-26T11:04:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-update-patient-ins/CodeSystem-fr-core-cs-v2-3307.xlsx
+++ b/ig/nr-update-patient-ins/CodeSystem-fr-core-cs-v2-3307.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-26T11:04:56+00:00</t>
+    <t>2024-02-26T11:06:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-update-patient-ins/CodeSystem-fr-core-cs-v2-3307.xlsx
+++ b/ig/nr-update-patient-ins/CodeSystem-fr-core-cs-v2-3307.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-26T11:06:19+00:00</t>
+    <t>2024-02-27T11:09:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-update-patient-ins/CodeSystem-fr-core-cs-v2-3307.xlsx
+++ b/ig/nr-update-patient-ins/CodeSystem-fr-core-cs-v2-3307.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-27T11:09:52+00:00</t>
+    <t>2024-02-27T11:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-update-patient-ins/CodeSystem-fr-core-cs-v2-3307.xlsx
+++ b/ig/nr-update-patient-ins/CodeSystem-fr-core-cs-v2-3307.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-27T11:11:58+00:00</t>
+    <t>2024-02-27T13:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
